--- a/insurance_forms/015_insurance_claim_discharge_form--insurance_forms.xlsx
+++ b/insurance_forms/015_insurance_claim_discharge_form--insurance_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Claimant Counselor Address</t>
+          <t>Claimant Counselor Provider Address</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Claimant Provider Address</t>
+          <t>Claimant Provider Provider Address</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Claimant Provider Address</t>
+          <t>Claimant Claimant Provider Address</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1253,8 +1253,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1282,12 +1282,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'id_card'}</t>
+          <t>id_card</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'ID card'}</t>
+          <t>ID card</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'claimant_statement'}</t>
+          <t>claimant_statement</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Claimant Statement'}</t>
+          <t>Claimant Statement</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'police_report'}</t>
+          <t>police_report</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Police Report'}</t>
+          <t>Police Report</t>
         </is>
       </c>
     </row>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'witness_statement'}</t>
+          <t>witness_statement</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Witness Statement'}</t>
+          <t>Witness Statement</t>
         </is>
       </c>
     </row>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1367,12 +1367,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'auto'}</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Auto'}</t>
+          <t>Auto</t>
         </is>
       </c>
     </row>
@@ -1401,12 +1401,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'home'}</t>
+          <t>home</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Home'}</t>
+          <t>Home</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'business'}</t>
+          <t>business</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Business'}</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
@@ -1435,12 +1435,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1452,12 +1452,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1469,12 +1469,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'canceled'}</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Canceled'}</t>
+          <t>Canceled</t>
         </is>
       </c>
     </row>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'dr'}</t>
+          <t>dr</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Dr'}</t>
+          <t>Dr</t>
         </is>
       </c>
     </row>
@@ -1520,12 +1520,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'hospital'}</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Hospital'}</t>
+          <t>Hospital</t>
         </is>
       </c>
     </row>
@@ -1537,12 +1537,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'clinic'}</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Clinic'}</t>
+          <t>Clinic</t>
         </is>
       </c>
     </row>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1571,12 +1571,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1588,12 +1588,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1605,12 +1605,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1622,12 +1622,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'dr'}</t>
+          <t>dr</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Dr'}</t>
+          <t>Dr</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'hospital'}</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Hospital'}</t>
+          <t>Hospital</t>
         </is>
       </c>
     </row>
@@ -1656,12 +1656,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'clinic'}</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Clinic'}</t>
+          <t>Clinic</t>
         </is>
       </c>
     </row>
@@ -1673,12 +1673,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1690,12 +1690,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'dr'}</t>
+          <t>dr</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Dr'}</t>
+          <t>Dr</t>
         </is>
       </c>
     </row>
@@ -1707,12 +1707,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'hospital'}</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Hospital'}</t>
+          <t>Hospital</t>
         </is>
       </c>
     </row>
@@ -1724,12 +1724,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'clinic'}</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'Clinic'}</t>
+          <t>Clinic</t>
         </is>
       </c>
     </row>
@@ -1741,12 +1741,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'dr'}</t>
+          <t>dr</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Dr'}</t>
+          <t>Dr</t>
         </is>
       </c>
     </row>
@@ -1775,12 +1775,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'hospital'}</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'Hospital'}</t>
+          <t>Hospital</t>
         </is>
       </c>
     </row>
@@ -1792,12 +1792,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'clinic'}</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'Clinic'}</t>
+          <t>Clinic</t>
         </is>
       </c>
     </row>
@@ -1809,12 +1809,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
